--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260527_214333.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260527_214333.xlsx
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260527_214333.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260527_214333.xlsx
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
